--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SalesTransactionMaintenanceRegist.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SalesTransactionMaintenanceRegist.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BS3.0\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28695" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="销售结算资金交易信息登记导入" sheetId="1" r:id="rId1"/>
@@ -15,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201">
-  <si>
-    <t>销售结算资金交易信息登记导入</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
   <si>
     <t>*提供销售结算资金服务机构代码</t>
   </si>
@@ -649,14 +651,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -679,165 +675,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -846,192 +696,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1112,17 +782,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1137,268 +796,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1428,84 +832,36 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1795,10 +1151,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
-  <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="30.75" style="10" customWidth="1"/>
     <col min="2" max="2" width="14.125" style="10" customWidth="1"/>
@@ -1817,1030 +1172,1014 @@
     <col min="16" max="16" width="13.375" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.25" spans="1:16">
+    <row r="1" spans="1:16" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="17"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="21" customHeight="1" spans="1:16">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="K1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="L1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="M1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="N1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="O1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="13" t="s">
+      <c r="P1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="6:6">
-      <c r="F19" s="16"/>
+    </row>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F18" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
-  </mergeCells>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1">
-      <formula1>各要素值域输入规则!$B$4:$B$41</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1 K3:K1048576">
-      <formula1>各要素值域输入规则!$A$2:$A$181</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="例如，该笔交易在2月2日8:30:02交易成功，则交易时间为083002" sqref="N1 N3:N1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F1048576">
-      <formula1>各要素值域输入规则!$B$2:$B$3</formula1>
-    </dataValidation>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1 K1"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="例如，该笔交易在2月2日8:30:02交易成功，则交易时间为083002" sqref="N2:N1048576"/>
   </dataValidations>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>各要素值域输入规则!$A$2:$A$181</xm:f>
+          </x14:formula1>
+          <xm:sqref>K2:K1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>各要素值域输入规则!$B$2:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C181"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="89.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="40.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52.5" customHeight="1" spans="1:2">
+    <row r="1" spans="1:2" ht="52.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A3" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" ht="14.25" spans="1:2">
-      <c r="A3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A4" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A5" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="5" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A6" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="5" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A7" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="5" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A8" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="5" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A9" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="5" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A10" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="5" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A11" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="5" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A12" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="5" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A13" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="5" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A14" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="5" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A15" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="5" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A16" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="5" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A17" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="5" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A18" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="5" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="5" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="5" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="5" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A22" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="5" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A23" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="5" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A24" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="5" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A25" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="5" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A26" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="5" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A27" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="5" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A28" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="5" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A29" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="5" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A30" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="5" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A31" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="5" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A32" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="5" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A33" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="5" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A34" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="5" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A35" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="5" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A36" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="5" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A37" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="5" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A38" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="5" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A39" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="5" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A40" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="5" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A41" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="5" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A42" s="5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="5" t="s">
+      <c r="C42" s="7"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A43" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C42" s="7"/>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="5" t="s">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A44" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="5" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A45" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="5" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A46" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="5" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A47" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="5" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A48" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="5" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A49" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="5" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A50" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="5" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A51" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="5" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A52" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="5" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A53" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="5" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A54" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="5" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A55" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="5" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A56" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="5" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A57" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="5" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A58" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="5" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A59" s="5" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="5" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A60" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="5" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A61" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="5" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A62" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="5" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A63" s="5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="5" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A64" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="5" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A65" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="5" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A66" s="5" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="5" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A67" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="5" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A68" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="5" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A69" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="5" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A70" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
-      <c r="A70" s="5" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A71" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="5" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A72" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="5" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A73" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
-      <c r="A73" s="5" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A74" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="5" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A75" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="5" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A76" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="5" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A77" s="5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="5" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A78" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
-      <c r="A78" s="5" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A79" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
-      <c r="A79" s="5" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A80" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="5" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A81" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="5" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A82" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="5" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A83" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="5" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A84" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="5" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A85" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="5" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A86" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="5" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A87" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="5" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A88" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="5" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A89" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
-      <c r="A89" s="5" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A90" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
-      <c r="A90" s="5" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A91" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
-      <c r="A91" s="5" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A92" s="5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="5" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A93" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="5" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A94" s="5" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
-      <c r="A94" s="5" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A95" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="5" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A96" s="5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="5" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A97" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="5" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A98" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
-      <c r="A98" s="5" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A99" s="5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
-      <c r="A99" s="5" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A100" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="5" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A101" s="5" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
-      <c r="A101" s="5" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A102" s="5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
-      <c r="A102" s="5" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A103" s="5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="5" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A104" s="5" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="5" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A105" s="5" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="5" t="s">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A106" s="5" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
-      <c r="A106" s="5" t="s">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A107" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="5" t="s">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A108" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="108" spans="1:1">
-      <c r="A108" s="5" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A109" s="5" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="5" t="s">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A110" s="5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="5" t="s">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A111" s="5" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="5" t="s">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A112" s="5" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="112" spans="1:1">
-      <c r="A112" s="5" t="s">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A113" s="5" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="5" t="s">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A114" s="5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="114" spans="1:1">
-      <c r="A114" s="5" t="s">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A115" s="5" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="115" spans="1:1">
-      <c r="A115" s="5" t="s">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A116" s="5" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="5" t="s">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A117" s="5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="5" t="s">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A118" s="5" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="5" t="s">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A119" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="5" t="s">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A120" s="5" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="5" t="s">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A121" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="5" t="s">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A122" s="5" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="5" t="s">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A123" s="5" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="5" t="s">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A124" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="5" t="s">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A125" s="5" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="5" t="s">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A126" s="5" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="5" t="s">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A127" s="5" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="5" t="s">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A128" s="5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="128" spans="1:1">
-      <c r="A128" s="5" t="s">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A129" s="5" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="5" t="s">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A130" s="5" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="5" t="s">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A131" s="5" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="131" spans="1:1">
-      <c r="A131" s="5" t="s">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A132" s="5" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="5" t="s">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A133" s="5" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="133" spans="1:1">
-      <c r="A133" s="5" t="s">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A134" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="134" spans="1:1">
-      <c r="A134" s="5" t="s">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A135" s="5" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="135" spans="1:1">
-      <c r="A135" s="5" t="s">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A136" s="5" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="136" spans="1:1">
-      <c r="A136" s="5" t="s">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A137" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="137" spans="1:1">
-      <c r="A137" s="5" t="s">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A138" s="5" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="138" spans="1:1">
-      <c r="A138" s="5" t="s">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A139" s="5" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="5" t="s">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A140" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="5" t="s">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A141" s="5" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="141" spans="1:1">
-      <c r="A141" s="5" t="s">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A142" s="5" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="5" t="s">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A143" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="143" spans="1:1">
-      <c r="A143" s="5" t="s">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A144" s="5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="144" spans="1:1">
-      <c r="A144" s="5" t="s">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A145" s="5" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="5" t="s">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A146" s="5" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="5" t="s">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A147" s="5" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="5" t="s">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A148" s="5" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="5" t="s">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A149" s="5" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="5" t="s">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A150" s="5" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="5" t="s">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A151" s="5" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="5" t="s">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A152" s="5" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="152" spans="1:1">
-      <c r="A152" s="5" t="s">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A153" s="5" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="153" spans="1:1">
-      <c r="A153" s="5" t="s">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A154" s="5" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="154" spans="1:1">
-      <c r="A154" s="5" t="s">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A155" s="5" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="155" spans="1:1">
-      <c r="A155" s="5" t="s">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A156" s="5" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="156" spans="1:1">
-      <c r="A156" s="5" t="s">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A157" s="5" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="157" spans="1:1">
-      <c r="A157" s="5" t="s">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A158" s="5" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="158" spans="1:1">
-      <c r="A158" s="5" t="s">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A159" s="5" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="159" spans="1:1">
-      <c r="A159" s="5" t="s">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A160" s="5" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="160" spans="1:1">
-      <c r="A160" s="5" t="s">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A161" s="5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="161" spans="1:1">
-      <c r="A161" s="5" t="s">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A162" s="5" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="162" spans="1:1">
-      <c r="A162" s="5" t="s">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A163" s="5" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="163" spans="1:1">
-      <c r="A163" s="5" t="s">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A164" s="5" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="164" spans="1:1">
-      <c r="A164" s="5" t="s">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A165" s="5" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="165" spans="1:1">
-      <c r="A165" s="5" t="s">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A166" s="5" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="166" spans="1:1">
-      <c r="A166" s="5" t="s">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A167" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="167" spans="1:1">
-      <c r="A167" s="5" t="s">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A168" s="5" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="168" spans="1:1">
-      <c r="A168" s="5" t="s">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A169" s="5" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="169" spans="1:1">
-      <c r="A169" s="5" t="s">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A170" s="5" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="170" spans="1:1">
-      <c r="A170" s="5" t="s">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A171" s="5" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="171" spans="1:1">
-      <c r="A171" s="5" t="s">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A172" s="5" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="172" spans="1:1">
-      <c r="A172" s="5" t="s">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A173" s="5" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="173" spans="1:1">
-      <c r="A173" s="5" t="s">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A174" s="5" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="174" spans="1:1">
-      <c r="A174" s="5" t="s">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A175" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="175" spans="1:1">
-      <c r="A175" s="5" t="s">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A176" s="5" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="176" spans="1:1">
-      <c r="A176" s="5" t="s">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A177" s="5" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="177" spans="1:1">
-      <c r="A177" s="5" t="s">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A178" s="5" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="178" spans="1:1">
-      <c r="A178" s="5" t="s">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A179" s="5" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="179" spans="1:1">
-      <c r="A179" s="5" t="s">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A180" s="8" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="180" spans="1:1">
-      <c r="A180" s="8" t="s">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A181" s="9" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="181" spans="1:1">
-      <c r="A181" s="9" t="s">
-        <v>200</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <headerFooter/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
 </worksheet>
 </file>